--- a/old_data.xlsx
+++ b/old_data.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="224" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="415" uniqueCount="119">
   <si>
     <t>txn_id</t>
   </si>
@@ -59,6 +59,12 @@
     <t>capital</t>
   </si>
   <si>
+    <t>bank charges</t>
+  </si>
+  <si>
+    <t>refund</t>
+  </si>
+  <si>
     <t>debit</t>
   </si>
   <si>
@@ -167,6 +173,60 @@
     <t>Destiny</t>
   </si>
   <si>
+    <t>Blessing</t>
+  </si>
+  <si>
+    <t>Loveth</t>
+  </si>
+  <si>
+    <t>Abigail</t>
+  </si>
+  <si>
+    <t>Rita</t>
+  </si>
+  <si>
+    <t>Chelsea</t>
+  </si>
+  <si>
+    <t>Jessica</t>
+  </si>
+  <si>
+    <t>Samantha</t>
+  </si>
+  <si>
+    <t>Hannah</t>
+  </si>
+  <si>
+    <t>Fati</t>
+  </si>
+  <si>
+    <t>Kimah</t>
+  </si>
+  <si>
+    <t>Vivian</t>
+  </si>
+  <si>
+    <t>Joy</t>
+  </si>
+  <si>
+    <t>Rachael</t>
+  </si>
+  <si>
+    <t>Zara</t>
+  </si>
+  <si>
+    <t>Chinonye</t>
+  </si>
+  <si>
+    <t>Eunice</t>
+  </si>
+  <si>
+    <t>Hafsat</t>
+  </si>
+  <si>
+    <t>Zohot</t>
+  </si>
+  <si>
     <t>Beauteous Lodge</t>
   </si>
   <si>
@@ -179,6 +239,9 @@
     <t>Tefund 2</t>
   </si>
   <si>
+    <t>Hostel B</t>
+  </si>
+  <si>
     <t>09025458334</t>
   </si>
   <si>
@@ -240,6 +303,69 @@
   </si>
   <si>
     <t>0806547428</t>
+  </si>
+  <si>
+    <t>09128574227</t>
+  </si>
+  <si>
+    <t>07043452364</t>
+  </si>
+  <si>
+    <t>09037695295</t>
+  </si>
+  <si>
+    <t>08121254628</t>
+  </si>
+  <si>
+    <t>09094498764</t>
+  </si>
+  <si>
+    <t>07040222475</t>
+  </si>
+  <si>
+    <t>09030325477</t>
+  </si>
+  <si>
+    <t>08103470120</t>
+  </si>
+  <si>
+    <t>09158837458</t>
+  </si>
+  <si>
+    <t>07078631601</t>
+  </si>
+  <si>
+    <t>0907604801</t>
+  </si>
+  <si>
+    <t>09088433985</t>
+  </si>
+  <si>
+    <t>09155335147</t>
+  </si>
+  <si>
+    <t>09158874301</t>
+  </si>
+  <si>
+    <t>09152361200</t>
+  </si>
+  <si>
+    <t>09038943331</t>
+  </si>
+  <si>
+    <t>09133611294</t>
+  </si>
+  <si>
+    <t>09161108802</t>
+  </si>
+  <si>
+    <t>09027398125</t>
+  </si>
+  <si>
+    <t>09032699772</t>
+  </si>
+  <si>
+    <t>07056713147</t>
   </si>
   <si>
     <t>CEO</t>
@@ -607,7 +733,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H44"/>
+  <dimension ref="A1:H82"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:8">
@@ -650,7 +776,7 @@
         <v>1200</v>
       </c>
       <c r="E2" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -667,7 +793,7 @@
         <v>500</v>
       </c>
       <c r="E3" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -684,13 +810,13 @@
         <v>4000</v>
       </c>
       <c r="E4" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="F4">
         <v>2</v>
       </c>
       <c r="G4" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="H4">
         <v>1</v>
@@ -710,13 +836,13 @@
         <v>2500</v>
       </c>
       <c r="E5" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="F5">
         <v>3</v>
       </c>
       <c r="G5" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="H5">
         <v>1</v>
@@ -736,13 +862,13 @@
         <v>2000</v>
       </c>
       <c r="E6" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="F6">
         <v>4</v>
       </c>
       <c r="G6" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="H6">
         <v>1</v>
@@ -762,13 +888,13 @@
         <v>2000</v>
       </c>
       <c r="E7" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="F7">
         <v>5</v>
       </c>
       <c r="G7" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="H7">
         <v>1</v>
@@ -788,13 +914,13 @@
         <v>2000</v>
       </c>
       <c r="E8" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="F8">
         <v>6</v>
       </c>
       <c r="G8" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="H8">
         <v>1</v>
@@ -814,13 +940,13 @@
         <v>3000</v>
       </c>
       <c r="E9" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="F9">
         <v>6</v>
       </c>
       <c r="G9" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="H9">
         <v>1</v>
@@ -840,13 +966,13 @@
         <v>2000</v>
       </c>
       <c r="E10" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="F10">
         <v>7</v>
       </c>
       <c r="G10" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="H10">
         <v>1</v>
@@ -866,13 +992,13 @@
         <v>2000</v>
       </c>
       <c r="E11" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="F11">
         <v>7</v>
       </c>
       <c r="G11" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="H11">
         <v>1</v>
@@ -892,13 +1018,13 @@
         <v>4000</v>
       </c>
       <c r="E12" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="F12">
         <v>7</v>
       </c>
       <c r="G12" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="H12">
         <v>2</v>
@@ -918,13 +1044,13 @@
         <v>3800</v>
       </c>
       <c r="E13" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="F13">
         <v>8</v>
       </c>
       <c r="G13" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="H13">
         <v>2</v>
@@ -944,13 +1070,13 @@
         <v>8000</v>
       </c>
       <c r="E14" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="F14">
         <v>9</v>
       </c>
       <c r="G14" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="H14">
         <v>1</v>
@@ -970,13 +1096,13 @@
         <v>10500</v>
       </c>
       <c r="E15" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="F15">
         <v>10</v>
       </c>
       <c r="G15" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="H15">
         <v>1</v>
@@ -996,13 +1122,13 @@
         <v>6000</v>
       </c>
       <c r="E16" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="F16">
         <v>11</v>
       </c>
       <c r="G16" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="H16">
         <v>1</v>
@@ -1022,13 +1148,13 @@
         <v>2000</v>
       </c>
       <c r="E17" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="F17">
         <v>12</v>
       </c>
       <c r="G17" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="H17">
         <v>1</v>
@@ -1048,13 +1174,13 @@
         <v>2000</v>
       </c>
       <c r="E18" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="F18">
         <v>12</v>
       </c>
       <c r="G18" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="H18">
         <v>1</v>
@@ -1074,13 +1200,13 @@
         <v>2000</v>
       </c>
       <c r="E19" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="F19">
         <v>12</v>
       </c>
       <c r="G19" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="H19">
         <v>1</v>
@@ -1100,13 +1226,13 @@
         <v>11000</v>
       </c>
       <c r="E20" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="F20">
         <v>12</v>
       </c>
       <c r="G20" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="H20">
         <v>2</v>
@@ -1126,13 +1252,13 @@
         <v>7000</v>
       </c>
       <c r="E21" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="F21">
         <v>13</v>
       </c>
       <c r="G21" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="H21">
         <v>1</v>
@@ -1152,13 +1278,13 @@
         <v>4000</v>
       </c>
       <c r="E22" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="F22">
         <v>14</v>
       </c>
       <c r="G22" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="H22">
         <v>2</v>
@@ -1178,13 +1304,13 @@
         <v>10000</v>
       </c>
       <c r="E23" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="F23">
         <v>15</v>
       </c>
       <c r="G23" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="H23">
         <v>1</v>
@@ -1204,13 +1330,13 @@
         <v>2000</v>
       </c>
       <c r="E24" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="F24">
         <v>16</v>
       </c>
       <c r="G24" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="H24">
         <v>1</v>
@@ -1230,13 +1356,13 @@
         <v>2000</v>
       </c>
       <c r="E25" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="F25">
         <v>16</v>
       </c>
       <c r="G25" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="H25">
         <v>1</v>
@@ -1256,13 +1382,13 @@
         <v>2000</v>
       </c>
       <c r="E26" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="F26">
         <v>16</v>
       </c>
       <c r="G26" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="H26">
         <v>1</v>
@@ -1282,13 +1408,13 @@
         <v>2000</v>
       </c>
       <c r="E27" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="F27">
         <v>17</v>
       </c>
       <c r="G27" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="H27">
         <v>1</v>
@@ -1308,13 +1434,13 @@
         <v>2000</v>
       </c>
       <c r="E28" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="F28">
         <v>18</v>
       </c>
       <c r="G28" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="H28">
         <v>1</v>
@@ -1334,13 +1460,13 @@
         <v>3000</v>
       </c>
       <c r="E29" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="F29">
         <v>19</v>
       </c>
       <c r="G29" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="H29">
         <v>1</v>
@@ -1360,13 +1486,13 @@
         <v>3000</v>
       </c>
       <c r="E30" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="F30">
         <v>19</v>
       </c>
       <c r="G30" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="H30">
         <v>1</v>
@@ -1386,13 +1512,13 @@
         <v>2000</v>
       </c>
       <c r="E31" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="F31">
         <v>20</v>
       </c>
       <c r="G31" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="H31">
         <v>1</v>
@@ -1412,13 +1538,13 @@
         <v>2000</v>
       </c>
       <c r="E32" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="F32">
         <v>20</v>
       </c>
       <c r="G32" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="H32">
         <v>1</v>
@@ -1438,7 +1564,7 @@
         <v>12000</v>
       </c>
       <c r="E33" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F33">
         <v>0</v>
@@ -1458,10 +1584,10 @@
         <v>6000</v>
       </c>
       <c r="E34" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="G34" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="H34">
         <v>12</v>
@@ -1481,10 +1607,10 @@
         <v>5000</v>
       </c>
       <c r="E35" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="G35" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="H35">
         <v>5</v>
@@ -1504,10 +1630,10 @@
         <v>8000</v>
       </c>
       <c r="E36" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="G36" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="H36">
         <v>2</v>
@@ -1527,10 +1653,10 @@
         <v>11200</v>
       </c>
       <c r="E37" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="G37" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="H37">
         <v>16</v>
@@ -1550,10 +1676,10 @@
         <v>25000</v>
       </c>
       <c r="E38" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="G38" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="H38">
         <v>5</v>
@@ -1573,10 +1699,10 @@
         <v>8100</v>
       </c>
       <c r="E39" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="G39" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="H39">
         <v>9</v>
@@ -1596,10 +1722,10 @@
         <v>6000</v>
       </c>
       <c r="E40" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="G40" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="H40">
         <v>4</v>
@@ -1619,10 +1745,10 @@
         <v>8000</v>
       </c>
       <c r="E41" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="G41" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="H41">
         <v>2</v>
@@ -1642,7 +1768,7 @@
         <v>5000</v>
       </c>
       <c r="E42" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F42">
         <v>0</v>
@@ -1662,7 +1788,7 @@
         <v>5000</v>
       </c>
       <c r="E43" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F43">
         <v>0</v>
@@ -1679,13 +1805,929 @@
         <v>13</v>
       </c>
       <c r="D44">
-        <v>78500</v>
+        <v>110550</v>
       </c>
       <c r="E44" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="F44">
         <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="1:8">
+      <c r="A45">
+        <v>44</v>
+      </c>
+      <c r="B45" s="2">
+        <v>46086</v>
+      </c>
+      <c r="C45" t="s">
+        <v>11</v>
+      </c>
+      <c r="D45">
+        <v>42000</v>
+      </c>
+      <c r="E45" t="s">
+        <v>16</v>
+      </c>
+      <c r="G45" t="s">
+        <v>18</v>
+      </c>
+      <c r="H45">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="46" spans="1:8">
+      <c r="A46">
+        <v>45</v>
+      </c>
+      <c r="B46" s="2">
+        <v>46086</v>
+      </c>
+      <c r="C46" t="s">
+        <v>11</v>
+      </c>
+      <c r="D46">
+        <v>11000</v>
+      </c>
+      <c r="E46" t="s">
+        <v>16</v>
+      </c>
+      <c r="G46" t="s">
+        <v>20</v>
+      </c>
+      <c r="H46">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="47" spans="1:8">
+      <c r="A47">
+        <v>46</v>
+      </c>
+      <c r="B47" s="2">
+        <v>46086</v>
+      </c>
+      <c r="C47" t="s">
+        <v>11</v>
+      </c>
+      <c r="D47">
+        <v>66000</v>
+      </c>
+      <c r="E47" t="s">
+        <v>16</v>
+      </c>
+      <c r="G47" t="s">
+        <v>22</v>
+      </c>
+      <c r="H47">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="48" spans="1:8">
+      <c r="A48">
+        <v>47</v>
+      </c>
+      <c r="B48" s="2">
+        <v>46086</v>
+      </c>
+      <c r="C48" t="s">
+        <v>9</v>
+      </c>
+      <c r="D48">
+        <v>4000</v>
+      </c>
+      <c r="E48" t="s">
+        <v>17</v>
+      </c>
+      <c r="F48">
+        <v>22</v>
+      </c>
+      <c r="G48" t="s">
+        <v>18</v>
+      </c>
+      <c r="H48">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="49" spans="1:8">
+      <c r="A49">
+        <v>48</v>
+      </c>
+      <c r="B49" s="2">
+        <v>46086</v>
+      </c>
+      <c r="C49" t="s">
+        <v>9</v>
+      </c>
+      <c r="D49">
+        <v>4000</v>
+      </c>
+      <c r="E49" t="s">
+        <v>17</v>
+      </c>
+      <c r="F49">
+        <v>15</v>
+      </c>
+      <c r="G49" t="s">
+        <v>18</v>
+      </c>
+      <c r="H49">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="50" spans="1:8">
+      <c r="A50">
+        <v>49</v>
+      </c>
+      <c r="B50" s="2">
+        <v>46086</v>
+      </c>
+      <c r="C50" t="s">
+        <v>9</v>
+      </c>
+      <c r="D50">
+        <v>2000</v>
+      </c>
+      <c r="E50" t="s">
+        <v>17</v>
+      </c>
+      <c r="F50">
+        <v>23</v>
+      </c>
+      <c r="G50" t="s">
+        <v>18</v>
+      </c>
+      <c r="H50">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="51" spans="1:8">
+      <c r="A51">
+        <v>50</v>
+      </c>
+      <c r="B51" s="2">
+        <v>46086</v>
+      </c>
+      <c r="C51" t="s">
+        <v>9</v>
+      </c>
+      <c r="D51">
+        <v>2000</v>
+      </c>
+      <c r="E51" t="s">
+        <v>17</v>
+      </c>
+      <c r="F51">
+        <v>24</v>
+      </c>
+      <c r="G51" t="s">
+        <v>18</v>
+      </c>
+      <c r="H51">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="52" spans="1:8">
+      <c r="A52">
+        <v>51</v>
+      </c>
+      <c r="B52" s="2">
+        <v>46086</v>
+      </c>
+      <c r="C52" t="s">
+        <v>9</v>
+      </c>
+      <c r="D52">
+        <v>2000</v>
+      </c>
+      <c r="E52" t="s">
+        <v>17</v>
+      </c>
+      <c r="F52">
+        <v>24</v>
+      </c>
+      <c r="G52" t="s">
+        <v>20</v>
+      </c>
+      <c r="H52">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="53" spans="1:8">
+      <c r="A53">
+        <v>52</v>
+      </c>
+      <c r="B53" s="2">
+        <v>46086</v>
+      </c>
+      <c r="C53" t="s">
+        <v>9</v>
+      </c>
+      <c r="D53">
+        <v>6000</v>
+      </c>
+      <c r="E53" t="s">
+        <v>17</v>
+      </c>
+      <c r="F53">
+        <v>25</v>
+      </c>
+      <c r="G53" t="s">
+        <v>18</v>
+      </c>
+      <c r="H53">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="54" spans="1:8">
+      <c r="A54">
+        <v>53</v>
+      </c>
+      <c r="B54" s="2">
+        <v>46086</v>
+      </c>
+      <c r="C54" t="s">
+        <v>9</v>
+      </c>
+      <c r="D54">
+        <v>2000</v>
+      </c>
+      <c r="E54" t="s">
+        <v>17</v>
+      </c>
+      <c r="F54">
+        <v>3</v>
+      </c>
+      <c r="G54" t="s">
+        <v>18</v>
+      </c>
+      <c r="H54">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="55" spans="1:8">
+      <c r="A55">
+        <v>54</v>
+      </c>
+      <c r="B55" s="2">
+        <v>46086</v>
+      </c>
+      <c r="C55" t="s">
+        <v>9</v>
+      </c>
+      <c r="D55">
+        <v>2000</v>
+      </c>
+      <c r="E55" t="s">
+        <v>17</v>
+      </c>
+      <c r="F55">
+        <v>26</v>
+      </c>
+      <c r="G55" t="s">
+        <v>18</v>
+      </c>
+      <c r="H55">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="56" spans="1:8">
+      <c r="A56">
+        <v>55</v>
+      </c>
+      <c r="B56" s="2">
+        <v>46086</v>
+      </c>
+      <c r="C56" t="s">
+        <v>8</v>
+      </c>
+      <c r="D56">
+        <v>1850</v>
+      </c>
+      <c r="E56" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="57" spans="1:8">
+      <c r="A57">
+        <v>56</v>
+      </c>
+      <c r="B57" s="2">
+        <v>46086</v>
+      </c>
+      <c r="C57" t="s">
+        <v>14</v>
+      </c>
+      <c r="D57">
+        <v>400</v>
+      </c>
+      <c r="E57" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="58" spans="1:8">
+      <c r="A58">
+        <v>57</v>
+      </c>
+      <c r="B58" s="2">
+        <v>46086</v>
+      </c>
+      <c r="C58" t="s">
+        <v>12</v>
+      </c>
+      <c r="D58">
+        <v>6600</v>
+      </c>
+      <c r="E58" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="59" spans="1:8">
+      <c r="A59">
+        <v>58</v>
+      </c>
+      <c r="B59" s="2">
+        <v>46087</v>
+      </c>
+      <c r="C59" t="s">
+        <v>15</v>
+      </c>
+      <c r="D59">
+        <v>5000</v>
+      </c>
+      <c r="E59" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="60" spans="1:8">
+      <c r="A60">
+        <v>59</v>
+      </c>
+      <c r="B60" s="2">
+        <v>46088</v>
+      </c>
+      <c r="C60" t="s">
+        <v>9</v>
+      </c>
+      <c r="D60">
+        <v>2500</v>
+      </c>
+      <c r="E60" t="s">
+        <v>17</v>
+      </c>
+      <c r="F60">
+        <v>27</v>
+      </c>
+      <c r="G60" t="s">
+        <v>18</v>
+      </c>
+      <c r="H60">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="61" spans="1:8">
+      <c r="A61">
+        <v>60</v>
+      </c>
+      <c r="B61" s="2">
+        <v>46088</v>
+      </c>
+      <c r="C61" t="s">
+        <v>9</v>
+      </c>
+      <c r="D61">
+        <v>2000</v>
+      </c>
+      <c r="E61" t="s">
+        <v>17</v>
+      </c>
+      <c r="F61">
+        <v>28</v>
+      </c>
+      <c r="G61" t="s">
+        <v>18</v>
+      </c>
+      <c r="H61">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="62" spans="1:8">
+      <c r="A62">
+        <v>61</v>
+      </c>
+      <c r="B62" s="2">
+        <v>46088</v>
+      </c>
+      <c r="C62" t="s">
+        <v>9</v>
+      </c>
+      <c r="D62">
+        <v>4000</v>
+      </c>
+      <c r="E62" t="s">
+        <v>17</v>
+      </c>
+      <c r="F62">
+        <v>29</v>
+      </c>
+      <c r="G62" t="s">
+        <v>18</v>
+      </c>
+      <c r="H62">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="63" spans="1:8">
+      <c r="A63">
+        <v>62</v>
+      </c>
+      <c r="B63" s="2">
+        <v>46088</v>
+      </c>
+      <c r="C63" t="s">
+        <v>9</v>
+      </c>
+      <c r="D63">
+        <v>2000</v>
+      </c>
+      <c r="E63" t="s">
+        <v>17</v>
+      </c>
+      <c r="F63">
+        <v>30</v>
+      </c>
+      <c r="G63" t="s">
+        <v>18</v>
+      </c>
+      <c r="H63">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="64" spans="1:8">
+      <c r="A64">
+        <v>63</v>
+      </c>
+      <c r="B64" s="2">
+        <v>46088</v>
+      </c>
+      <c r="C64" t="s">
+        <v>9</v>
+      </c>
+      <c r="D64">
+        <v>2000</v>
+      </c>
+      <c r="E64" t="s">
+        <v>17</v>
+      </c>
+      <c r="F64">
+        <v>31</v>
+      </c>
+      <c r="G64" t="s">
+        <v>18</v>
+      </c>
+      <c r="H64">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="65" spans="1:8">
+      <c r="A65">
+        <v>64</v>
+      </c>
+      <c r="B65" s="2">
+        <v>46088</v>
+      </c>
+      <c r="C65" t="s">
+        <v>9</v>
+      </c>
+      <c r="D65">
+        <v>2000</v>
+      </c>
+      <c r="E65" t="s">
+        <v>17</v>
+      </c>
+      <c r="F65">
+        <v>31</v>
+      </c>
+      <c r="G65" t="s">
+        <v>20</v>
+      </c>
+      <c r="H65">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="66" spans="1:8">
+      <c r="A66">
+        <v>65</v>
+      </c>
+      <c r="B66" s="2">
+        <v>46088</v>
+      </c>
+      <c r="C66" t="s">
+        <v>9</v>
+      </c>
+      <c r="D66">
+        <v>4000</v>
+      </c>
+      <c r="E66" t="s">
+        <v>17</v>
+      </c>
+      <c r="F66">
+        <v>32</v>
+      </c>
+      <c r="G66" t="s">
+        <v>18</v>
+      </c>
+      <c r="H66">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="67" spans="1:8">
+      <c r="A67">
+        <v>66</v>
+      </c>
+      <c r="B67" s="2">
+        <v>46088</v>
+      </c>
+      <c r="C67" t="s">
+        <v>9</v>
+      </c>
+      <c r="D67">
+        <v>4000</v>
+      </c>
+      <c r="E67" t="s">
+        <v>17</v>
+      </c>
+      <c r="F67">
+        <v>33</v>
+      </c>
+      <c r="G67" t="s">
+        <v>18</v>
+      </c>
+      <c r="H67">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="68" spans="1:8">
+      <c r="A68">
+        <v>69</v>
+      </c>
+      <c r="B68" s="2">
+        <v>46088</v>
+      </c>
+      <c r="C68" t="s">
+        <v>9</v>
+      </c>
+      <c r="D68">
+        <v>4000</v>
+      </c>
+      <c r="E68" t="s">
+        <v>17</v>
+      </c>
+      <c r="F68">
+        <v>34</v>
+      </c>
+      <c r="G68" t="s">
+        <v>18</v>
+      </c>
+      <c r="H68">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="69" spans="1:8">
+      <c r="A69">
+        <v>70</v>
+      </c>
+      <c r="B69" s="2">
+        <v>46088</v>
+      </c>
+      <c r="C69" t="s">
+        <v>9</v>
+      </c>
+      <c r="D69">
+        <v>2000</v>
+      </c>
+      <c r="E69" t="s">
+        <v>17</v>
+      </c>
+      <c r="F69">
+        <v>34</v>
+      </c>
+      <c r="G69" t="s">
+        <v>20</v>
+      </c>
+      <c r="H69">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="70" spans="1:8">
+      <c r="A70">
+        <v>71</v>
+      </c>
+      <c r="B70" s="2">
+        <v>46088</v>
+      </c>
+      <c r="C70" t="s">
+        <v>9</v>
+      </c>
+      <c r="D70">
+        <v>10000</v>
+      </c>
+      <c r="E70" t="s">
+        <v>17</v>
+      </c>
+      <c r="F70">
+        <v>35</v>
+      </c>
+      <c r="G70" t="s">
+        <v>22</v>
+      </c>
+      <c r="H70">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="71" spans="1:8">
+      <c r="A71">
+        <v>72</v>
+      </c>
+      <c r="B71" s="2">
+        <v>46088</v>
+      </c>
+      <c r="C71" t="s">
+        <v>9</v>
+      </c>
+      <c r="D71">
+        <v>4000</v>
+      </c>
+      <c r="E71" t="s">
+        <v>17</v>
+      </c>
+      <c r="F71">
+        <v>36</v>
+      </c>
+      <c r="G71" t="s">
+        <v>18</v>
+      </c>
+      <c r="H71">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="72" spans="1:8">
+      <c r="A72">
+        <v>73</v>
+      </c>
+      <c r="B72" s="2">
+        <v>46088</v>
+      </c>
+      <c r="C72" t="s">
+        <v>9</v>
+      </c>
+      <c r="D72">
+        <v>2000</v>
+      </c>
+      <c r="E72" t="s">
+        <v>17</v>
+      </c>
+      <c r="F72">
+        <v>37</v>
+      </c>
+      <c r="G72" t="s">
+        <v>20</v>
+      </c>
+      <c r="H72">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="73" spans="1:8">
+      <c r="A73">
+        <v>74</v>
+      </c>
+      <c r="B73" s="2">
+        <v>46088</v>
+      </c>
+      <c r="C73" t="s">
+        <v>9</v>
+      </c>
+      <c r="D73">
+        <v>12000</v>
+      </c>
+      <c r="E73" t="s">
+        <v>17</v>
+      </c>
+      <c r="F73">
+        <v>37</v>
+      </c>
+      <c r="G73" t="s">
+        <v>22</v>
+      </c>
+      <c r="H73">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="74" spans="1:8">
+      <c r="A74">
+        <v>75</v>
+      </c>
+      <c r="B74" s="2">
+        <v>46088</v>
+      </c>
+      <c r="C74" t="s">
+        <v>9</v>
+      </c>
+      <c r="D74">
+        <v>5000</v>
+      </c>
+      <c r="E74" t="s">
+        <v>17</v>
+      </c>
+      <c r="F74">
+        <v>38</v>
+      </c>
+      <c r="G74" t="s">
+        <v>24</v>
+      </c>
+      <c r="H74">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="75" spans="1:8">
+      <c r="A75">
+        <v>76</v>
+      </c>
+      <c r="B75" s="2">
+        <v>46088</v>
+      </c>
+      <c r="C75" t="s">
+        <v>9</v>
+      </c>
+      <c r="D75">
+        <v>2000</v>
+      </c>
+      <c r="E75" t="s">
+        <v>17</v>
+      </c>
+      <c r="F75">
+        <v>38</v>
+      </c>
+      <c r="G75" t="s">
+        <v>18</v>
+      </c>
+      <c r="H75">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="76" spans="1:8">
+      <c r="A76">
+        <v>77</v>
+      </c>
+      <c r="B76" s="2">
+        <v>46088</v>
+      </c>
+      <c r="C76" t="s">
+        <v>9</v>
+      </c>
+      <c r="D76">
+        <v>4000</v>
+      </c>
+      <c r="E76" t="s">
+        <v>17</v>
+      </c>
+      <c r="F76">
+        <v>39</v>
+      </c>
+      <c r="G76" t="s">
+        <v>18</v>
+      </c>
+      <c r="H76">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="77" spans="1:8">
+      <c r="A77">
+        <v>78</v>
+      </c>
+      <c r="B77" s="2">
+        <v>46088</v>
+      </c>
+      <c r="C77" t="s">
+        <v>9</v>
+      </c>
+      <c r="D77">
+        <v>4000</v>
+      </c>
+      <c r="E77" t="s">
+        <v>17</v>
+      </c>
+      <c r="F77">
+        <v>40</v>
+      </c>
+      <c r="G77" t="s">
+        <v>18</v>
+      </c>
+      <c r="H77">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="78" spans="1:8">
+      <c r="A78">
+        <v>79</v>
+      </c>
+      <c r="B78" s="2">
+        <v>46088</v>
+      </c>
+      <c r="C78" t="s">
+        <v>9</v>
+      </c>
+      <c r="D78">
+        <v>2000</v>
+      </c>
+      <c r="E78" t="s">
+        <v>17</v>
+      </c>
+      <c r="F78">
+        <v>41</v>
+      </c>
+      <c r="G78" t="s">
+        <v>18</v>
+      </c>
+      <c r="H78">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="79" spans="1:8">
+      <c r="A79">
+        <v>80</v>
+      </c>
+      <c r="B79" s="2">
+        <v>46088</v>
+      </c>
+      <c r="C79" t="s">
+        <v>9</v>
+      </c>
+      <c r="D79">
+        <v>10000</v>
+      </c>
+      <c r="E79" t="s">
+        <v>17</v>
+      </c>
+      <c r="F79">
+        <v>42</v>
+      </c>
+      <c r="G79" t="s">
+        <v>22</v>
+      </c>
+      <c r="H79">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="80" spans="1:8">
+      <c r="A80">
+        <v>81</v>
+      </c>
+      <c r="B80" s="2">
+        <v>46088</v>
+      </c>
+      <c r="C80" t="s">
+        <v>14</v>
+      </c>
+      <c r="D80">
+        <v>20</v>
+      </c>
+      <c r="E80" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="81" spans="1:5">
+      <c r="A81">
+        <v>82</v>
+      </c>
+      <c r="B81" s="2">
+        <v>46088</v>
+      </c>
+      <c r="C81" t="s">
+        <v>8</v>
+      </c>
+      <c r="D81">
+        <v>500</v>
+      </c>
+      <c r="E81" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="82" spans="1:5">
+      <c r="A82">
+        <v>83</v>
+      </c>
+      <c r="B82" s="2">
+        <v>46088</v>
+      </c>
+      <c r="C82" t="s">
+        <v>12</v>
+      </c>
+      <c r="D82">
+        <v>5000</v>
+      </c>
+      <c r="E82" t="s">
+        <v>16</v>
       </c>
     </row>
   </sheetData>
@@ -1695,7 +2737,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F23"/>
+  <dimension ref="A1:F44"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:6">
@@ -1703,19 +2745,19 @@
         <v>5</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
     </row>
     <row r="2" spans="1:6">
@@ -1723,13 +2765,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="C2" t="s">
-        <v>50</v>
+        <v>70</v>
       </c>
       <c r="F2" t="s">
-        <v>75</v>
+        <v>117</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -1737,19 +2779,19 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C3" t="s">
-        <v>51</v>
+        <v>71</v>
       </c>
       <c r="D3" s="2">
         <v>46081</v>
       </c>
       <c r="E3" t="s">
-        <v>54</v>
+        <v>75</v>
       </c>
       <c r="F3" t="s">
-        <v>76</v>
+        <v>118</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -1757,19 +2799,19 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="C4" t="s">
-        <v>51</v>
+        <v>71</v>
       </c>
       <c r="D4" s="2">
         <v>46081</v>
       </c>
       <c r="E4" t="s">
-        <v>55</v>
+        <v>76</v>
       </c>
       <c r="F4" t="s">
-        <v>76</v>
+        <v>118</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -1777,19 +2819,19 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="C5" t="s">
-        <v>51</v>
+        <v>71</v>
       </c>
       <c r="D5" s="2">
         <v>46081</v>
       </c>
       <c r="E5" t="s">
-        <v>56</v>
+        <v>77</v>
       </c>
       <c r="F5" t="s">
-        <v>76</v>
+        <v>118</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -1797,19 +2839,19 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C6" t="s">
-        <v>51</v>
+        <v>71</v>
       </c>
       <c r="D6" s="2">
         <v>46081</v>
       </c>
       <c r="E6" t="s">
-        <v>57</v>
+        <v>78</v>
       </c>
       <c r="F6" t="s">
-        <v>76</v>
+        <v>118</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -1817,19 +2859,19 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="C7" t="s">
-        <v>52</v>
+        <v>72</v>
       </c>
       <c r="D7" s="2">
         <v>46081</v>
       </c>
       <c r="E7" t="s">
-        <v>58</v>
+        <v>79</v>
       </c>
       <c r="F7" t="s">
-        <v>76</v>
+        <v>118</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -1837,19 +2879,19 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="C8" t="s">
-        <v>52</v>
+        <v>72</v>
       </c>
       <c r="D8" s="2">
         <v>46081</v>
       </c>
       <c r="E8" t="s">
-        <v>59</v>
+        <v>80</v>
       </c>
       <c r="F8" t="s">
-        <v>76</v>
+        <v>118</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -1857,19 +2899,19 @@
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="C9" t="s">
-        <v>52</v>
+        <v>72</v>
       </c>
       <c r="D9" s="2">
         <v>46081</v>
       </c>
       <c r="E9" t="s">
-        <v>60</v>
+        <v>81</v>
       </c>
       <c r="F9" t="s">
-        <v>76</v>
+        <v>118</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -1877,19 +2919,19 @@
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="C10" t="s">
-        <v>52</v>
+        <v>72</v>
       </c>
       <c r="D10" s="2">
         <v>46081</v>
       </c>
       <c r="E10" t="s">
-        <v>61</v>
+        <v>82</v>
       </c>
       <c r="F10" t="s">
-        <v>76</v>
+        <v>118</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -1897,19 +2939,19 @@
         <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C11" t="s">
-        <v>52</v>
+        <v>72</v>
       </c>
       <c r="D11" s="2">
         <v>46081</v>
       </c>
       <c r="E11" t="s">
-        <v>62</v>
+        <v>83</v>
       </c>
       <c r="F11" t="s">
-        <v>76</v>
+        <v>118</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -1917,19 +2959,19 @@
         <v>10</v>
       </c>
       <c r="B12" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="C12" t="s">
-        <v>52</v>
+        <v>72</v>
       </c>
       <c r="D12" s="2">
         <v>46081</v>
       </c>
       <c r="E12" t="s">
-        <v>63</v>
+        <v>84</v>
       </c>
       <c r="F12" t="s">
-        <v>76</v>
+        <v>118</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -1937,19 +2979,19 @@
         <v>11</v>
       </c>
       <c r="B13" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="C13" t="s">
-        <v>52</v>
+        <v>72</v>
       </c>
       <c r="D13" s="2">
         <v>46081</v>
       </c>
       <c r="E13" t="s">
-        <v>64</v>
+        <v>85</v>
       </c>
       <c r="F13" t="s">
-        <v>76</v>
+        <v>118</v>
       </c>
     </row>
     <row r="14" spans="1:6">
@@ -1957,19 +2999,19 @@
         <v>12</v>
       </c>
       <c r="B14" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="C14" t="s">
-        <v>52</v>
+        <v>72</v>
       </c>
       <c r="D14" s="2">
         <v>46081</v>
       </c>
       <c r="E14" t="s">
-        <v>65</v>
+        <v>86</v>
       </c>
       <c r="F14" t="s">
-        <v>76</v>
+        <v>118</v>
       </c>
     </row>
     <row r="15" spans="1:6">
@@ -1977,19 +3019,19 @@
         <v>13</v>
       </c>
       <c r="B15" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="C15" t="s">
-        <v>52</v>
+        <v>72</v>
       </c>
       <c r="D15" s="2">
         <v>46081</v>
       </c>
       <c r="E15" t="s">
-        <v>66</v>
+        <v>87</v>
       </c>
       <c r="F15" t="s">
-        <v>76</v>
+        <v>118</v>
       </c>
     </row>
     <row r="16" spans="1:6">
@@ -1997,19 +3039,19 @@
         <v>14</v>
       </c>
       <c r="B16" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="C16" t="s">
-        <v>52</v>
+        <v>72</v>
       </c>
       <c r="D16" s="2">
         <v>46081</v>
       </c>
       <c r="E16" t="s">
-        <v>67</v>
+        <v>88</v>
       </c>
       <c r="F16" t="s">
-        <v>76</v>
+        <v>118</v>
       </c>
     </row>
     <row r="17" spans="1:6">
@@ -2017,19 +3059,19 @@
         <v>15</v>
       </c>
       <c r="B17" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="C17" t="s">
-        <v>52</v>
+        <v>72</v>
       </c>
       <c r="D17" s="2">
         <v>46081</v>
       </c>
       <c r="E17" t="s">
-        <v>68</v>
+        <v>89</v>
       </c>
       <c r="F17" t="s">
-        <v>76</v>
+        <v>118</v>
       </c>
     </row>
     <row r="18" spans="1:6">
@@ -2037,19 +3079,19 @@
         <v>16</v>
       </c>
       <c r="B18" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="C18" t="s">
-        <v>50</v>
+        <v>70</v>
       </c>
       <c r="D18" s="2">
         <v>46081</v>
       </c>
       <c r="E18" t="s">
-        <v>69</v>
+        <v>90</v>
       </c>
       <c r="F18" t="s">
-        <v>76</v>
+        <v>118</v>
       </c>
     </row>
     <row r="19" spans="1:6">
@@ -2057,19 +3099,19 @@
         <v>17</v>
       </c>
       <c r="B19" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="C19" t="s">
-        <v>53</v>
+        <v>73</v>
       </c>
       <c r="D19" s="2">
         <v>46083</v>
       </c>
       <c r="E19" t="s">
-        <v>70</v>
+        <v>91</v>
       </c>
       <c r="F19" t="s">
-        <v>76</v>
+        <v>118</v>
       </c>
     </row>
     <row r="20" spans="1:6">
@@ -2077,19 +3119,19 @@
         <v>18</v>
       </c>
       <c r="B20" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="C20" t="s">
-        <v>53</v>
+        <v>73</v>
       </c>
       <c r="D20" s="2">
         <v>46083</v>
       </c>
       <c r="E20" t="s">
-        <v>71</v>
+        <v>92</v>
       </c>
       <c r="F20" t="s">
-        <v>76</v>
+        <v>118</v>
       </c>
     </row>
     <row r="21" spans="1:6">
@@ -2097,19 +3139,19 @@
         <v>19</v>
       </c>
       <c r="B21" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="C21" t="s">
-        <v>53</v>
+        <v>73</v>
       </c>
       <c r="D21" s="2">
         <v>46083</v>
       </c>
       <c r="E21" t="s">
-        <v>72</v>
+        <v>93</v>
       </c>
       <c r="F21" t="s">
-        <v>76</v>
+        <v>118</v>
       </c>
     </row>
     <row r="22" spans="1:6">
@@ -2117,19 +3159,19 @@
         <v>20</v>
       </c>
       <c r="B22" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="C22" t="s">
-        <v>53</v>
+        <v>73</v>
       </c>
       <c r="D22" s="2">
         <v>46083</v>
       </c>
       <c r="E22" t="s">
-        <v>73</v>
+        <v>94</v>
       </c>
       <c r="F22" t="s">
-        <v>76</v>
+        <v>118</v>
       </c>
     </row>
     <row r="23" spans="1:6">
@@ -2137,19 +3179,439 @@
         <v>21</v>
       </c>
       <c r="B23" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="C23" t="s">
-        <v>53</v>
+        <v>73</v>
       </c>
       <c r="D23" s="2">
         <v>46083</v>
       </c>
       <c r="E23" t="s">
+        <v>95</v>
+      </c>
+      <c r="F23" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6">
+      <c r="A24">
+        <v>22</v>
+      </c>
+      <c r="B24" t="s">
+        <v>52</v>
+      </c>
+      <c r="C24" t="s">
+        <v>72</v>
+      </c>
+      <c r="D24" s="2">
+        <v>46086</v>
+      </c>
+      <c r="E24" t="s">
+        <v>96</v>
+      </c>
+      <c r="F24" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6">
+      <c r="A25">
+        <v>23</v>
+      </c>
+      <c r="B25" t="s">
+        <v>53</v>
+      </c>
+      <c r="C25" t="s">
+        <v>72</v>
+      </c>
+      <c r="D25" s="2">
+        <v>46086</v>
+      </c>
+      <c r="E25" t="s">
+        <v>97</v>
+      </c>
+      <c r="F25" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6">
+      <c r="A26">
+        <v>24</v>
+      </c>
+      <c r="B26" t="s">
+        <v>54</v>
+      </c>
+      <c r="C26" t="s">
+        <v>72</v>
+      </c>
+      <c r="D26" s="2">
+        <v>46086</v>
+      </c>
+      <c r="E26" t="s">
+        <v>98</v>
+      </c>
+      <c r="F26" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6">
+      <c r="A27">
+        <v>25</v>
+      </c>
+      <c r="B27" t="s">
+        <v>55</v>
+      </c>
+      <c r="C27" t="s">
+        <v>72</v>
+      </c>
+      <c r="D27" s="2">
+        <v>46086</v>
+      </c>
+      <c r="E27" t="s">
+        <v>99</v>
+      </c>
+      <c r="F27" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6">
+      <c r="A28">
+        <v>26</v>
+      </c>
+      <c r="B28" t="s">
+        <v>56</v>
+      </c>
+      <c r="C28" t="s">
+        <v>71</v>
+      </c>
+      <c r="D28" s="2">
+        <v>46086</v>
+      </c>
+      <c r="E28" t="s">
+        <v>100</v>
+      </c>
+      <c r="F28" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6">
+      <c r="A29">
+        <v>27</v>
+      </c>
+      <c r="B29" t="s">
+        <v>45</v>
+      </c>
+      <c r="C29" t="s">
         <v>74</v>
       </c>
-      <c r="F23" t="s">
-        <v>76</v>
+      <c r="D29" s="2">
+        <v>46088</v>
+      </c>
+      <c r="E29" t="s">
+        <v>101</v>
+      </c>
+      <c r="F29" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6">
+      <c r="A30">
+        <v>28</v>
+      </c>
+      <c r="B30" t="s">
+        <v>57</v>
+      </c>
+      <c r="C30" t="s">
+        <v>74</v>
+      </c>
+      <c r="D30" s="2">
+        <v>46088</v>
+      </c>
+      <c r="E30" t="s">
+        <v>102</v>
+      </c>
+      <c r="F30" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6">
+      <c r="A31">
+        <v>29</v>
+      </c>
+      <c r="B31" t="s">
+        <v>44</v>
+      </c>
+      <c r="C31" t="s">
+        <v>74</v>
+      </c>
+      <c r="D31" s="2">
+        <v>46088</v>
+      </c>
+      <c r="E31" t="s">
+        <v>103</v>
+      </c>
+      <c r="F31" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6">
+      <c r="A32">
+        <v>30</v>
+      </c>
+      <c r="B32" t="s">
+        <v>58</v>
+      </c>
+      <c r="C32" t="s">
+        <v>74</v>
+      </c>
+      <c r="D32" s="2">
+        <v>46088</v>
+      </c>
+      <c r="E32" t="s">
+        <v>104</v>
+      </c>
+      <c r="F32" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6">
+      <c r="A33">
+        <v>31</v>
+      </c>
+      <c r="B33" t="s">
+        <v>59</v>
+      </c>
+      <c r="C33" t="s">
+        <v>74</v>
+      </c>
+      <c r="D33" s="2">
+        <v>46088</v>
+      </c>
+      <c r="E33" t="s">
+        <v>105</v>
+      </c>
+      <c r="F33" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6">
+      <c r="A34">
+        <v>32</v>
+      </c>
+      <c r="B34" t="s">
+        <v>60</v>
+      </c>
+      <c r="C34" t="s">
+        <v>74</v>
+      </c>
+      <c r="D34" s="2">
+        <v>46088</v>
+      </c>
+      <c r="E34" t="s">
+        <v>106</v>
+      </c>
+      <c r="F34" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6">
+      <c r="A35">
+        <v>33</v>
+      </c>
+      <c r="B35" t="s">
+        <v>61</v>
+      </c>
+      <c r="C35" t="s">
+        <v>74</v>
+      </c>
+      <c r="D35" s="2">
+        <v>46088</v>
+      </c>
+      <c r="E35" t="s">
+        <v>107</v>
+      </c>
+      <c r="F35" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6">
+      <c r="A36">
+        <v>34</v>
+      </c>
+      <c r="B36" t="s">
+        <v>62</v>
+      </c>
+      <c r="C36" t="s">
+        <v>74</v>
+      </c>
+      <c r="D36" s="2">
+        <v>46088</v>
+      </c>
+      <c r="E36" t="s">
+        <v>108</v>
+      </c>
+      <c r="F36" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6">
+      <c r="A37">
+        <v>35</v>
+      </c>
+      <c r="B37" t="s">
+        <v>63</v>
+      </c>
+      <c r="C37" t="s">
+        <v>74</v>
+      </c>
+      <c r="D37" s="2">
+        <v>46088</v>
+      </c>
+      <c r="E37" t="s">
+        <v>109</v>
+      </c>
+      <c r="F37" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6">
+      <c r="A38">
+        <v>36</v>
+      </c>
+      <c r="B38" t="s">
+        <v>64</v>
+      </c>
+      <c r="C38" t="s">
+        <v>74</v>
+      </c>
+      <c r="D38" s="2">
+        <v>46088</v>
+      </c>
+      <c r="E38" t="s">
+        <v>110</v>
+      </c>
+      <c r="F38" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6">
+      <c r="A39">
+        <v>37</v>
+      </c>
+      <c r="B39" t="s">
+        <v>65</v>
+      </c>
+      <c r="C39" t="s">
+        <v>74</v>
+      </c>
+      <c r="D39" s="2">
+        <v>46088</v>
+      </c>
+      <c r="E39" t="s">
+        <v>111</v>
+      </c>
+      <c r="F39" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6">
+      <c r="A40">
+        <v>38</v>
+      </c>
+      <c r="B40" t="s">
+        <v>66</v>
+      </c>
+      <c r="C40" t="s">
+        <v>74</v>
+      </c>
+      <c r="D40" s="2">
+        <v>46088</v>
+      </c>
+      <c r="E40" t="s">
+        <v>112</v>
+      </c>
+      <c r="F40" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6">
+      <c r="A41">
+        <v>39</v>
+      </c>
+      <c r="B41" t="s">
+        <v>67</v>
+      </c>
+      <c r="C41" t="s">
+        <v>74</v>
+      </c>
+      <c r="D41" s="2">
+        <v>46088</v>
+      </c>
+      <c r="E41" t="s">
+        <v>113</v>
+      </c>
+      <c r="F41" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6">
+      <c r="A42">
+        <v>40</v>
+      </c>
+      <c r="B42" t="s">
+        <v>45</v>
+      </c>
+      <c r="C42" t="s">
+        <v>74</v>
+      </c>
+      <c r="D42" s="2">
+        <v>46088</v>
+      </c>
+      <c r="E42" t="s">
+        <v>114</v>
+      </c>
+      <c r="F42" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6">
+      <c r="A43">
+        <v>41</v>
+      </c>
+      <c r="B43" t="s">
+        <v>68</v>
+      </c>
+      <c r="C43" t="s">
+        <v>74</v>
+      </c>
+      <c r="D43" s="2">
+        <v>46088</v>
+      </c>
+      <c r="E43" t="s">
+        <v>115</v>
+      </c>
+      <c r="F43" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6">
+      <c r="A44">
+        <v>42</v>
+      </c>
+      <c r="B44" t="s">
+        <v>69</v>
+      </c>
+      <c r="C44" t="s">
+        <v>72</v>
+      </c>
+      <c r="D44" s="2">
+        <v>46088</v>
+      </c>
+      <c r="E44" t="s">
+        <v>116</v>
+      </c>
+      <c r="F44" t="s">
+        <v>118</v>
       </c>
     </row>
   </sheetData>

--- a/old_data.xlsx
+++ b/old_data.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="415" uniqueCount="119">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="418" uniqueCount="119">
   <si>
     <t>txn_id</t>
   </si>
@@ -733,7 +733,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H82"/>
+  <dimension ref="A1:H83"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:8">
@@ -2158,6 +2158,9 @@
       <c r="E59" t="s">
         <v>17</v>
       </c>
+      <c r="F59">
+        <v>0</v>
+      </c>
     </row>
     <row r="60" spans="1:8">
       <c r="A60">
@@ -2525,7 +2528,7 @@
     </row>
     <row r="74" spans="1:8">
       <c r="A74">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B74" s="2">
         <v>46088</v>
@@ -2534,7 +2537,7 @@
         <v>9</v>
       </c>
       <c r="D74">
-        <v>5000</v>
+        <v>2000</v>
       </c>
       <c r="E74" t="s">
         <v>17</v>
@@ -2543,7 +2546,7 @@
         <v>38</v>
       </c>
       <c r="G74" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="H74">
         <v>1</v>
@@ -2551,7 +2554,7 @@
     </row>
     <row r="75" spans="1:8">
       <c r="A75">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B75" s="2">
         <v>46088</v>
@@ -2560,24 +2563,24 @@
         <v>9</v>
       </c>
       <c r="D75">
-        <v>2000</v>
+        <v>4000</v>
       </c>
       <c r="E75" t="s">
         <v>17</v>
       </c>
       <c r="F75">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G75" t="s">
         <v>18</v>
       </c>
       <c r="H75">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="76" spans="1:8">
       <c r="A76">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="B76" s="2">
         <v>46088</v>
@@ -2592,7 +2595,7 @@
         <v>17</v>
       </c>
       <c r="F76">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="G76" t="s">
         <v>18</v>
@@ -2603,7 +2606,7 @@
     </row>
     <row r="77" spans="1:8">
       <c r="A77">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B77" s="2">
         <v>46088</v>
@@ -2612,24 +2615,24 @@
         <v>9</v>
       </c>
       <c r="D77">
-        <v>4000</v>
+        <v>2000</v>
       </c>
       <c r="E77" t="s">
         <v>17</v>
       </c>
       <c r="F77">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="G77" t="s">
         <v>18</v>
       </c>
       <c r="H77">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="78" spans="1:8">
       <c r="A78">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B78" s="2">
         <v>46088</v>
@@ -2638,16 +2641,16 @@
         <v>9</v>
       </c>
       <c r="D78">
-        <v>2000</v>
+        <v>10000</v>
       </c>
       <c r="E78" t="s">
         <v>17</v>
       </c>
       <c r="F78">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="G78" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="H78">
         <v>1</v>
@@ -2655,79 +2658,102 @@
     </row>
     <row r="79" spans="1:8">
       <c r="A79">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B79" s="2">
         <v>46088</v>
       </c>
       <c r="C79" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="D79">
-        <v>10000</v>
+        <v>20</v>
       </c>
       <c r="E79" t="s">
-        <v>17</v>
-      </c>
-      <c r="F79">
-        <v>42</v>
-      </c>
-      <c r="G79" t="s">
-        <v>22</v>
-      </c>
-      <c r="H79">
-        <v>1</v>
+        <v>16</v>
       </c>
     </row>
     <row r="80" spans="1:8">
       <c r="A80">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B80" s="2">
         <v>46088</v>
       </c>
       <c r="C80" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="D80">
-        <v>20</v>
+        <v>500</v>
       </c>
       <c r="E80" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="81" spans="1:5">
+    <row r="81" spans="1:8">
       <c r="A81">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B81" s="2">
         <v>46088</v>
       </c>
       <c r="C81" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="D81">
-        <v>500</v>
+        <v>5000</v>
       </c>
       <c r="E81" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="82" spans="1:5">
+    <row r="82" spans="1:8">
       <c r="A82">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B82" s="2">
-        <v>46088</v>
+        <v>46089</v>
       </c>
       <c r="C82" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D82">
-        <v>5000</v>
+        <v>24500</v>
       </c>
       <c r="E82" t="s">
         <v>16</v>
+      </c>
+      <c r="G82" t="s">
+        <v>18</v>
+      </c>
+      <c r="H82">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="83" spans="1:8">
+      <c r="A83">
+        <v>85</v>
+      </c>
+      <c r="B83" s="2">
+        <v>46089</v>
+      </c>
+      <c r="C83" t="s">
+        <v>9</v>
+      </c>
+      <c r="D83">
+        <v>6000</v>
+      </c>
+      <c r="E83" t="s">
+        <v>17</v>
+      </c>
+      <c r="F83">
+        <v>16</v>
+      </c>
+      <c r="G83" t="s">
+        <v>18</v>
+      </c>
+      <c r="H83">
+        <v>3</v>
       </c>
     </row>
   </sheetData>
